--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486445_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486445_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0216</v>
+        <v>3.6671</v>
       </c>
       <c r="E2" t="n">
-        <v>5.6652</v>
+        <v>5.2182</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.6436</v>
+        <v>-1.5511</v>
       </c>
       <c r="G2" t="n">
         <v>2.3469</v>
@@ -610,13 +610,13 @@
         <v>2.1751</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5447</v>
+        <v>0.1902</v>
       </c>
       <c r="T2" t="n">
-        <v>1.4817</v>
+        <v>1.0347</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9370000000000001</v>
+        <v>-0.8445</v>
       </c>
       <c r="V2" t="n">
         <v>1.13</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.0535</v>
+        <v>0.7183</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3675</v>
+        <v>1.0322</v>
       </c>
       <c r="F3" t="n">
         <v>-0.314</v>
@@ -688,10 +688,10 @@
         <v>1.9576</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6321</v>
+        <v>0.2968</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5432</v>
+        <v>0.2079</v>
       </c>
       <c r="U3" t="n">
         <v>0.08890000000000001</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.1684</v>
+        <v>-0.0258</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0605</v>
+        <v>0.0513</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1079</v>
+        <v>-0.0771</v>
       </c>
       <c r="G4" t="n">
         <v>-0.5555</v>
@@ -766,13 +766,13 @@
         <v>0.6525</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2655</v>
+        <v>-0.1229</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.137</v>
+        <v>-0.0252</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1285</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.4212</v>
+        <v>-0.6254</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4458</v>
+        <v>-0.5575</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0245</v>
+        <v>-0.0679</v>
       </c>
       <c r="G5" t="n">
         <v>-1.4896</v>
@@ -844,13 +844,13 @@
         <v>1.305</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1114</v>
+        <v>-0.09279999999999999</v>
       </c>
       <c r="T5" t="n">
-        <v>0.08409999999999999</v>
+        <v>-0.0276</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0273</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>0.7395</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. STILMA</t>
+          <t>C. DIAZ RODRIGUEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.6165</v>
+        <v>-1.5645</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2802</v>
+        <v>-0.064</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3363</v>
+        <v>-1.5005</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.8257</v>
+        <v>3.3486</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6479</v>
+        <v>-0.1584</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.1778</v>
+        <v>3.507</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.4773</v>
+        <v>5.9793</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1.7519</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.4773</v>
+        <v>4.2274</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3484</v>
+        <v>-2.6307</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6479</v>
+        <v>-1.9103</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.7004</v>
+        <v>-0.7204</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-4.7852</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.0875</v>
+        <v>-6.5252</v>
       </c>
       <c r="R6" t="n">
-        <v>1.0875</v>
+        <v>1.7401</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9694</v>
+        <v>-0.128</v>
       </c>
       <c r="T6" t="n">
-        <v>1.2846</v>
+        <v>0.4819</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3152</v>
+        <v>-0.6099</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.7602</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CRUZ UCEDA</t>
+          <t>J. EZQUERRA TRELLES</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.9696</v>
+        <v>-2.2663</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3595</v>
+        <v>-1.5997</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3291</v>
+        <v>-0.6666</v>
       </c>
       <c r="G7" t="n">
-        <v>-5.7222</v>
+        <v>-2.2068</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.1165</v>
+        <v>-0.8577</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.6058</v>
+        <v>-1.3491</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.5951</v>
+        <v>-0.5914</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2397</v>
+        <v>-0.3253</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.3554</v>
+        <v>-0.2661</v>
       </c>
       <c r="M7" t="n">
-        <v>-4.1272</v>
+        <v>-1.6153</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.8768</v>
+        <v>-0.5324</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.2504</v>
+        <v>-1.0829</v>
       </c>
       <c r="P7" t="n">
-        <v>0.87</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
         <v>-1.0875</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9576</v>
+        <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6874</v>
+        <v>-0.0595</v>
       </c>
       <c r="T7" t="n">
-        <v>2.8468</v>
+        <v>0.0793</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1595</v>
+        <v>-0.1388</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1952</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. DIAZ RODRIGUEZ</t>
+          <t>M. STILMA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.5087</v>
+        <v>-2.3795</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0698</v>
+        <v>-0.9508</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4388</v>
+        <v>-1.4287</v>
       </c>
       <c r="G8" t="n">
-        <v>3.3486</v>
+        <v>-1.8257</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1584</v>
+        <v>-0.6479</v>
       </c>
       <c r="I8" t="n">
-        <v>3.507</v>
+        <v>-1.1778</v>
       </c>
       <c r="J8" t="n">
-        <v>5.9793</v>
+        <v>-0.4773</v>
       </c>
       <c r="K8" t="n">
-        <v>1.7519</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>4.2274</v>
+        <v>-0.4773</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.6307</v>
+        <v>-1.3484</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.9103</v>
+        <v>-0.6479</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.7204</v>
+        <v>-0.7004</v>
       </c>
       <c r="P8" t="n">
-        <v>-4.7852</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>-6.5252</v>
+        <v>-1.0875</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7401</v>
+        <v>1.0875</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0722</v>
+        <v>0.2064</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5239</v>
+        <v>0.6141</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5482</v>
+        <v>-0.4077</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.7602</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. EZQUERRA TRELLES</t>
+          <t>J. BERGSTEDT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.01</v>
+        <v>-3.6582</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1585</v>
+        <v>-2.5707</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.8515</v>
+        <v>-1.0876</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2068</v>
+        <v>-1.7833</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8577</v>
+        <v>-1.2438</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.3491</v>
+        <v>-0.5395</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5914</v>
+        <v>-0.5194</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3253</v>
+        <v>-0.5959</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.2661</v>
+        <v>0.0765</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6153</v>
+        <v>-1.2639</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5324</v>
+        <v>-0.6479</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0829</v>
+        <v>-0.616</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.7401</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.1751</v>
       </c>
       <c r="R9" t="n">
-        <v>1.0875</v>
+        <v>0.435</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.8032</v>
+        <v>-0.1349</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.4795</v>
+        <v>0.1238</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3237</v>
+        <v>-0.2587</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BERGSTEDT</t>
+          <t>J. GARCIA SANCHEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.6775</v>
+        <v>-3.6606</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.6824</v>
+        <v>-1.2812</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9951</v>
+        <v>-2.3795</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.7833</v>
+        <v>-0.3493</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.2438</v>
+        <v>-1.539</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5395</v>
+        <v>1.1897</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.5194</v>
+        <v>1.5801</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5959</v>
+        <v>-0.1611</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0765</v>
+        <v>1.7412</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2639</v>
+        <v>-1.9293</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6479</v>
+        <v>-1.3779</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.616</v>
+        <v>-0.5514</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.7401</v>
+        <v>-2.3926</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.1751</v>
+        <v>-3.2626</v>
       </c>
       <c r="R10" t="n">
-        <v>0.435</v>
+        <v>0.87</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1542</v>
+        <v>0.2112</v>
       </c>
       <c r="T10" t="n">
-        <v>0.012</v>
+        <v>0.4014</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1662</v>
+        <v>-0.1902</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>J. GARCIA SANCHEZ</t>
+          <t>I. CRUZ UCEDA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9265</v>
+        <v>-3.75</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3929</v>
+        <v>-1.2052</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.5336</v>
+        <v>-2.5448</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.3493</v>
+        <v>-5.7222</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.539</v>
+        <v>-2.1165</v>
       </c>
       <c r="I11" t="n">
-        <v>1.1897</v>
+        <v>-3.6058</v>
       </c>
       <c r="J11" t="n">
-        <v>1.5801</v>
+        <v>-1.5951</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1611</v>
+        <v>-0.2397</v>
       </c>
       <c r="L11" t="n">
-        <v>1.7412</v>
+        <v>-1.3554</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.9293</v>
+        <v>-4.1272</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3779</v>
+        <v>-1.8768</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5514</v>
+        <v>-2.2504</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.3926</v>
+        <v>0.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.2626</v>
+        <v>-1.0875</v>
       </c>
       <c r="R11" t="n">
-        <v>0.87</v>
+        <v>1.9576</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0547</v>
+        <v>0.907</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2896</v>
+        <v>1.2822</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3443</v>
+        <v>-0.3752</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.13</v>
+        <v>0.1952</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.3751</v>
+        <v>-3.928</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.7454</v>
+        <v>-1.2983</v>
       </c>
       <c r="F12" t="n">
         <v>-2.6297</v>
@@ -1390,10 +1390,10 @@
         <v>1.9576</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.697</v>
+        <v>-0.2499</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4879</v>
+        <v>-0.0408</v>
       </c>
       <c r="U12" t="n">
         <v>-0.2091</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.2015</v>
+        <v>-6.3267</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.7828</v>
+        <v>-5.0005</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4186</v>
+        <v>-1.3262</v>
       </c>
       <c r="G13" t="n">
         <v>-6.3062</v>
@@ -1468,13 +1468,13 @@
         <v>1.0875</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.8528</v>
+        <v>0.0219</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8099</v>
+        <v>-0.0276</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0429</v>
+        <v>0.0496</v>
       </c>
       <c r="V13" t="n">
         <v>-1.13</v>
@@ -1501,10 +1501,10 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-23.7999</v>
+        <v>-23.7996</v>
       </c>
       <c r="E14" t="n">
-        <v>-8.226100000000001</v>
+        <v>-8.226199999999999</v>
       </c>
       <c r="F14" t="n">
         <v>-15.5737</v>
@@ -1519,16 +1519,16 @@
         <v>-7.0283</v>
       </c>
       <c r="J14" t="n">
-        <v>6.834600000000001</v>
+        <v>6.834599999999999</v>
       </c>
       <c r="K14" t="n">
         <v>1.766</v>
       </c>
       <c r="L14" t="n">
-        <v>5.068399999999999</v>
+        <v>5.068400000000002</v>
       </c>
       <c r="M14" t="n">
-        <v>-25.2225</v>
+        <v>-25.22250000000001</v>
       </c>
       <c r="N14" t="n">
         <v>-13.1259</v>
@@ -1546,10 +1546,10 @@
         <v>16.313</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0454</v>
+        <v>1.0455</v>
       </c>
       <c r="T14" t="n">
-        <v>4.103800000000001</v>
+        <v>4.1041</v>
       </c>
       <c r="U14" t="n">
         <v>-3.0584</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Y. BARRUETA</t>
+          <t>S. QUINTELA SALVADOR</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>5.6198</v>
+        <v>6.3334</v>
       </c>
       <c r="E15" t="n">
-        <v>3.1488</v>
+        <v>4.2432</v>
       </c>
       <c r="F15" t="n">
-        <v>2.471</v>
+        <v>2.0902</v>
       </c>
       <c r="G15" t="n">
-        <v>3.0477</v>
+        <v>4.2881</v>
       </c>
       <c r="H15" t="n">
-        <v>2.5122</v>
+        <v>3.3638</v>
       </c>
       <c r="I15" t="n">
-        <v>0.5355</v>
+        <v>0.9243</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0463</v>
+        <v>4.1639</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8136</v>
+        <v>2.9016</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2327</v>
+        <v>1.2622</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0014</v>
+        <v>0.1242</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3013</v>
+        <v>0.4621</v>
       </c>
       <c r="O15" t="n">
-        <v>0.3028</v>
+        <v>-0.3379</v>
       </c>
       <c r="P15" t="n">
-        <v>1.305</v>
+        <v>1.7401</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0875</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3926</v>
+        <v>1.7401</v>
       </c>
       <c r="S15" t="n">
-        <v>1.2671</v>
+        <v>0.3052</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0601</v>
+        <v>0.0793</v>
       </c>
       <c r="U15" t="n">
-        <v>1.207</v>
+        <v>0.2259</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. QUINTELA SALVADOR</t>
+          <t>Y. BARRUETA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.5999</v>
+        <v>5.0419</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6844</v>
+        <v>3.3723</v>
       </c>
       <c r="F16" t="n">
-        <v>1.9155</v>
+        <v>1.6696</v>
       </c>
       <c r="G16" t="n">
-        <v>4.2881</v>
+        <v>3.0477</v>
       </c>
       <c r="H16" t="n">
-        <v>3.3638</v>
+        <v>2.5122</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9243</v>
+        <v>0.5355</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1639</v>
+        <v>3.0463</v>
       </c>
       <c r="K16" t="n">
-        <v>2.9016</v>
+        <v>2.8136</v>
       </c>
       <c r="L16" t="n">
-        <v>1.2622</v>
+        <v>0.2327</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1242</v>
+        <v>0.0014</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4621</v>
+        <v>-0.3013</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.3379</v>
+        <v>0.3028</v>
       </c>
       <c r="P16" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.0875</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7401</v>
+        <v>2.3926</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4283</v>
+        <v>0.6892</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4795</v>
+        <v>0.2836</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0512</v>
+        <v>0.4056</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.1968</v>
+        <v>4.4742</v>
       </c>
       <c r="E17" t="n">
         <v>4.8198</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.623</v>
+        <v>-0.3456</v>
       </c>
       <c r="G17" t="n">
         <v>6.7677</v>
@@ -1780,13 +1780,13 @@
         <v>2.1751</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7655999999999999</v>
+        <v>-0.4882</v>
       </c>
       <c r="T17" t="n">
         <v>0.3461</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.1117</v>
+        <v>-0.8343</v>
       </c>
       <c r="V17" t="n">
         <v>0.3698</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.9868</v>
+        <v>4.1268</v>
       </c>
       <c r="E18" t="n">
-        <v>3.8381</v>
+        <v>3.2793</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1487</v>
+        <v>0.8474</v>
       </c>
       <c r="G18" t="n">
         <v>2.8979</v>
@@ -1858,13 +1858,13 @@
         <v>2.3926</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0633</v>
+        <v>0.0766</v>
       </c>
       <c r="T18" t="n">
-        <v>1.1596</v>
+        <v>0.6009</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.223</v>
+        <v>-0.5242</v>
       </c>
       <c r="V18" t="n">
         <v>0.9347</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.8167</v>
+        <v>3.3291</v>
       </c>
       <c r="E19" t="n">
-        <v>2.7922</v>
+        <v>2.904</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0244</v>
+        <v>0.4251</v>
       </c>
       <c r="G19" t="n">
         <v>2.743</v>
@@ -1936,13 +1936,13 @@
         <v>1.9576</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7964</v>
+        <v>-0.2839</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2776</v>
+        <v>0.3894</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.074</v>
+        <v>-0.6733</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. DE SOUSA ANJO BRITO</t>
+          <t>D. KRAVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.7464</v>
+        <v>1.9862</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0186</v>
+        <v>0.571</v>
       </c>
       <c r="F20" t="n">
-        <v>0.7278</v>
+        <v>1.4152</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1845</v>
+        <v>3.3769</v>
       </c>
       <c r="H20" t="n">
-        <v>1.469</v>
+        <v>2.6095</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2845</v>
+        <v>0.7674</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1057</v>
+        <v>3.5866</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3719</v>
+        <v>2.2478</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2661</v>
+        <v>1.3387</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9213</v>
+        <v>-0.2097</v>
       </c>
       <c r="N20" t="n">
-        <v>0.09710000000000001</v>
+        <v>0.3617</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0184</v>
+        <v>-0.5714</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2175</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9576</v>
+        <v>1.5225</v>
       </c>
       <c r="S20" t="n">
-        <v>1.5842</v>
+        <v>-0.3683</v>
       </c>
       <c r="T20" t="n">
-        <v>1.8927</v>
+        <v>-0.1009</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3085</v>
+        <v>-0.2674</v>
       </c>
       <c r="V20" t="n">
-        <v>0.1952</v>
+        <v>-0.3698</v>
       </c>
       <c r="W20" t="n">
-        <v>0.1952</v>
+        <v>-0.7395</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.3698</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. KRAVIC</t>
+          <t>F. DOS ANJOS DE PAULA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3028</v>
+        <v>0.8973</v>
       </c>
       <c r="E21" t="n">
-        <v>0.124</v>
+        <v>0.3352</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1788</v>
+        <v>0.5621</v>
       </c>
       <c r="G21" t="n">
-        <v>3.3769</v>
+        <v>-0.6475</v>
       </c>
       <c r="H21" t="n">
-        <v>2.6095</v>
+        <v>-0.4347</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7674</v>
+        <v>-0.2128</v>
       </c>
       <c r="J21" t="n">
-        <v>3.5866</v>
+        <v>0.6587</v>
       </c>
       <c r="K21" t="n">
-        <v>2.2478</v>
+        <v>0.4292</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3387</v>
+        <v>0.2295</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2097</v>
+        <v>-1.3062</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3617</v>
+        <v>-0.8639</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5714</v>
+        <v>-0.4423</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6525</v>
+        <v>-0</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5225</v>
+        <v>2.1751</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0517</v>
+        <v>0.2196</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.548</v>
+        <v>0.5264</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5038</v>
+        <v>-0.3067</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3698</v>
+        <v>1.3252</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7395</v>
+        <v>1.3252</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3698</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.1967</v>
+        <v>0.8756</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.1011</v>
+        <v>-1.3246</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2978</v>
+        <v>2.2002</v>
       </c>
       <c r="G22" t="n">
         <v>-0.4059</v>
@@ -2170,13 +2170,13 @@
         <v>1.5225</v>
       </c>
       <c r="S22" t="n">
-        <v>0.428</v>
+        <v>0.1069</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4146</v>
+        <v>0.1911</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0134</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="V22" t="n">
         <v>0.7395</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>F. DOS ANJOS DE PAULA</t>
+          <t>A. GRELA ROJAS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.7548</v>
+        <v>0.6194</v>
       </c>
       <c r="E23" t="n">
-        <v>0.2235</v>
+        <v>0.0182</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5313</v>
+        <v>0.6011</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6475</v>
+        <v>0.4653</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.4347</v>
+        <v>0.1673</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.2128</v>
+        <v>0.298</v>
       </c>
       <c r="J23" t="n">
-        <v>0.6587</v>
+        <v>0.0182</v>
       </c>
       <c r="K23" t="n">
-        <v>0.4292</v>
+        <v>0.0182</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2295</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.3062</v>
+        <v>0.447</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8639</v>
+        <v>0.149</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.4423</v>
+        <v>0.298</v>
       </c>
       <c r="P23" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>2.1751</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0.077</v>
+        <v>0.1541</v>
       </c>
       <c r="T23" t="n">
-        <v>0.4146</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3376</v>
+        <v>0.1541</v>
       </c>
       <c r="V23" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.3252</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2269,7 +2269,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. GRELA ROJAS</t>
+          <t>D. DE SOUSA ANJO BRITO</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,64 +2281,64 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5269</v>
+        <v>0.5993000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0182</v>
+        <v>-0.2108</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5087</v>
+        <v>0.8101</v>
       </c>
       <c r="G24" t="n">
-        <v>0.4653</v>
+        <v>0.1845</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1673</v>
+        <v>1.469</v>
       </c>
       <c r="I24" t="n">
-        <v>0.298</v>
+        <v>-1.2845</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0182</v>
+        <v>1.1057</v>
       </c>
       <c r="K24" t="n">
-        <v>0.0182</v>
+        <v>1.3719</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>-0.2661</v>
       </c>
       <c r="M24" t="n">
-        <v>0.447</v>
+        <v>-0.9213</v>
       </c>
       <c r="N24" t="n">
-        <v>0.149</v>
+        <v>0.09710000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>0.298</v>
+        <v>-1.0184</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.9576</v>
       </c>
       <c r="S24" t="n">
-        <v>0.0616</v>
+        <v>0.4371</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>0.6633</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0616</v>
+        <v>-0.2262</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>0.1952</v>
       </c>
       <c r="X24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9478</v>
+        <v>-2.9934</v>
       </c>
       <c r="E25" t="n">
-        <v>-2.993</v>
+        <v>-2.4342</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.9549</v>
+        <v>-0.5593</v>
       </c>
       <c r="G25" t="n">
         <v>-4.3297</v>
@@ -2404,13 +2404,13 @@
         <v>1.7401</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3582</v>
+        <v>-0.4038</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.4795</v>
+        <v>0.0793</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.8787</v>
+        <v>-0.4831</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>23.7998</v>
+        <v>25.2898</v>
       </c>
       <c r="E26" t="n">
-        <v>15.5735</v>
+        <v>15.5734</v>
       </c>
       <c r="F26" t="n">
-        <v>8.226099999999999</v>
+        <v>9.716100000000001</v>
       </c>
       <c r="G26" t="n">
         <v>18.388</v>
@@ -2464,7 +2464,7 @@
         <v>12.0964</v>
       </c>
       <c r="M26" t="n">
-        <v>-6.834600000000001</v>
+        <v>-6.8346</v>
       </c>
       <c r="N26" t="n">
         <v>-1.7661</v>
@@ -2482,13 +2482,13 @@
         <v>19.5758</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.0456</v>
+        <v>0.4445000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>3.0583</v>
+        <v>3.0585</v>
       </c>
       <c r="U26" t="n">
-        <v>-4.1041</v>
+        <v>-2.613700000000001</v>
       </c>
       <c r="V26" t="n">
         <v>3.1946</v>
